--- a/Objetivos/Objetivos-modelo.xlsx
+++ b/Objetivos/Objetivos-modelo.xlsx
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="363">
   <si>
     <t xml:space="preserve">Objetivos da qualidade — Como usar esta planilha</t>
   </si>
@@ -906,6 +906,9 @@
     <t xml:space="preserve">Rever a escala do pico com a entrega dos novos condomínios, em março.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mais dois entregadores extras nas sextas e nos sábados</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estudar a compra do segundo forno, segundo item do Pareto dos atrasos.</t>
   </si>
   <si>
@@ -1056,7 +1059,7 @@
     <t xml:space="preserve">Gerente comercial</t>
   </si>
   <si>
-    <t xml:space="preserve">Manter 96% das entregas na data confirmada.</t>
+    <t xml:space="preserve">Manter 97% das entregas na data confirmada.</t>
   </si>
   <si>
     <t xml:space="preserve">Requisito legal ou contratual</t>
@@ -1119,7 +1122,7 @@
     <t xml:space="preserve">Refugo total, todo mês.</t>
   </si>
   <si>
-    <t xml:space="preserve">Visitar o cliente A e combinar um plano conjunto.</t>
+    <t xml:space="preserve">Fazer a segunda visita ao cliente A e rever o plano conjunto.</t>
   </si>
   <si>
     <t xml:space="preserve">Uma visita</t>
@@ -1176,7 +1179,7 @@
     <t xml:space="preserve">Processos auditados, todo mês.</t>
   </si>
   <si>
-    <t xml:space="preserve">Homologar o fornecedor de resina reciclada.</t>
+    <t xml:space="preserve">Homologar o segundo fornecedor de resina, que oferece a resina reciclada.</t>
   </si>
   <si>
     <t xml:space="preserve">Ensaios externos: R$ 12.000</t>
@@ -1874,11 +1877,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="80437280"/>
-        <c:axId val="97915134"/>
+        <c:axId val="6793122"/>
+        <c:axId val="15333995"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80437280"/>
+        <c:axId val="6793122"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1910,7 +1913,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97915134"/>
+        <c:crossAx val="15333995"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1918,7 +1921,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97915134"/>
+        <c:axId val="15333995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1959,7 +1962,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80437280"/>
+        <c:crossAx val="6793122"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -3252,6 +3255,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14:K25" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O compromisso da política a que o objetivo responde" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D14:D25" type="list">
       <formula1>"C1,C2,C3,C4"</formula1>
       <formula2>0</formula2>
@@ -3271,10 +3278,6 @@
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I14:J25" type="decimal">
       <formula1>-1000000000</formula1>
       <formula2>1000000000</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14:K25" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -6949,7 +6952,7 @@
         <v>73</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F20" s="35" t="n">
         <v>3.9</v>
@@ -7054,7 +7057,7 @@
       </c>
       <c r="L24" s="38"/>
     </row>
-    <row r="25" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="s">
         <v>107</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>250</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>141</v>
+        <v>251</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="36" t="n">
@@ -7089,10 +7092,10 @@
         <v>107</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="36" t="n">
@@ -7110,7 +7113,7 @@
         <v>239</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L26" s="7"/>
     </row>
@@ -7119,10 +7122,10 @@
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="36" t="n">
@@ -7140,7 +7143,7 @@
         <v>231</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L27" s="7"/>
     </row>
@@ -7149,10 +7152,10 @@
         <v>108</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="36" t="n">
@@ -7170,7 +7173,7 @@
         <v>242</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L28" s="7"/>
     </row>
@@ -7179,10 +7182,10 @@
         <v>109</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="36" t="n">
@@ -7200,7 +7203,7 @@
         <v>231</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" s="7"/>
     </row>
@@ -7209,7 +7212,7 @@
         <v>109</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>234</v>
@@ -7230,7 +7233,7 @@
         <v>242</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -7239,7 +7242,7 @@
         <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>234</v>
@@ -7260,7 +7263,7 @@
         <v>239</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -7269,10 +7272,10 @@
         <v>111</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="36" t="n">
@@ -7290,7 +7293,7 @@
         <v>242</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L32" s="7"/>
     </row>
@@ -7299,10 +7302,10 @@
         <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="36" t="n">
@@ -7314,13 +7317,13 @@
         <v>Atrasada</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>242</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L33" s="7"/>
     </row>
@@ -7329,10 +7332,10 @@
         <v>113</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="36" t="n">
@@ -7350,7 +7353,7 @@
         <v>239</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L34" s="7"/>
     </row>
@@ -7359,10 +7362,10 @@
         <v>113</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="36" t="n">
@@ -7380,7 +7383,7 @@
         <v>242</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L35" s="7"/>
     </row>
@@ -7435,7 +7438,7 @@
         <v>107</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D39" s="35" t="n">
         <v>95</v>
@@ -7469,7 +7472,7 @@
         <v>108</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D40" s="35" t="n">
         <v>1.9</v>
@@ -7503,7 +7506,7 @@
         <v>109</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D41" s="35" t="s">
         <v>234</v>
@@ -7537,7 +7540,7 @@
         <v>110</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D42" s="35" t="n">
         <v>1.6</v>
@@ -7571,7 +7574,7 @@
         <v>111</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D43" s="35" t="n">
         <v>5</v>
@@ -7605,7 +7608,7 @@
         <v>112</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D44" s="35" t="n">
         <v>3.9</v>
@@ -7639,7 +7642,7 @@
         <v>113</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D45" s="35" t="s">
         <v>234</v>
@@ -7721,7 +7724,7 @@
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
@@ -7939,7 +7942,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -7956,7 +7959,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -7973,7 +7976,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -7990,7 +7993,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -8024,7 +8027,7 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -8041,7 +8044,7 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -8058,7 +8061,7 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -8124,7 +8127,7 @@
         <v>107</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>77</v>
@@ -8142,10 +8145,10 @@
         <v>46752</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K15" s="34" t="s">
         <v>232</v>
@@ -8160,7 +8163,7 @@
         <v>108</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>75</v>
@@ -8178,10 +8181,10 @@
         <v>46568</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K16" s="34" t="s">
         <v>232</v>
@@ -8196,25 +8199,25 @@
         <v>109</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>97</v>
       </c>
       <c r="G17" s="35" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" s="36" t="n">
         <v>46752</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>142</v>
@@ -8232,7 +8235,7 @@
         <v>110</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>75</v>
@@ -8250,10 +8253,10 @@
         <v>46738</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K18" s="34" t="s">
         <v>227</v>
@@ -8268,7 +8271,7 @@
         <v>111</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>77</v>
@@ -8286,10 +8289,10 @@
         <v>46660</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K19" s="34" t="s">
         <v>227</v>
@@ -8304,7 +8307,7 @@
         <v>112</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>77</v>
@@ -8322,10 +8325,10 @@
         <v>46568</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K20" s="34" t="s">
         <v>232</v>
@@ -8340,13 +8343,13 @@
         <v>113</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>100</v>
@@ -8358,10 +8361,10 @@
         <v>46752</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K21" s="34" t="s">
         <v>227</v>
@@ -8420,10 +8423,10 @@
         <v>107</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="36" t="n">
@@ -8438,10 +8441,10 @@
         <v>24</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L25" s="7"/>
     </row>
@@ -8450,10 +8453,10 @@
         <v>107</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="36" t="n">
@@ -8468,10 +8471,10 @@
         <v>24</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L26" s="7"/>
     </row>
@@ -8480,10 +8483,10 @@
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="36" t="n">
@@ -8498,10 +8501,10 @@
         <v>143</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L27" s="7"/>
     </row>
@@ -8510,10 +8513,10 @@
         <v>108</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="36" t="n">
@@ -8528,10 +8531,10 @@
         <v>24</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L28" s="7"/>
     </row>
@@ -8540,7 +8543,7 @@
         <v>109</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>234</v>
@@ -8558,10 +8561,10 @@
         <v>143</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L29" s="7"/>
     </row>
@@ -8570,10 +8573,10 @@
         <v>110</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="36" t="n">
@@ -8588,10 +8591,10 @@
         <v>143</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -8600,10 +8603,10 @@
         <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="36" t="n">
@@ -8618,10 +8621,10 @@
         <v>143</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -8630,10 +8633,10 @@
         <v>110</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="36" t="n">
@@ -8648,22 +8651,22 @@
         <v>24</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="8" t="s">
         <v>111</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="36" t="n">
@@ -8678,10 +8681,10 @@
         <v>143</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L33" s="7"/>
     </row>
@@ -8690,10 +8693,10 @@
         <v>111</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="36" t="n">
@@ -8708,10 +8711,10 @@
         <v>143</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L34" s="7"/>
     </row>
@@ -8720,10 +8723,10 @@
         <v>111</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="36" t="n">
@@ -8735,13 +8738,13 @@
         <v>Não iniciada</v>
       </c>
       <c r="I35" s="39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L35" s="7"/>
     </row>
@@ -8750,7 +8753,7 @@
         <v>112</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>234</v>
@@ -8768,10 +8771,10 @@
         <v>143</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L36" s="7"/>
     </row>
@@ -8780,7 +8783,7 @@
         <v>113</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>234</v>
@@ -8795,13 +8798,13 @@
         <v>Não iniciada</v>
       </c>
       <c r="I37" s="39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L37" s="7"/>
     </row>
@@ -8860,7 +8863,7 @@
         <v>107</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D41" s="35" t="n">
         <v>2.5</v>
@@ -8898,7 +8901,7 @@
         <v>108</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D42" s="35" t="n">
         <v>58</v>
@@ -8936,7 +8939,7 @@
         <v>109</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D43" s="35" t="n">
         <v>97</v>
@@ -8974,7 +8977,7 @@
         <v>110</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D44" s="35" t="n">
         <v>0</v>
@@ -9012,7 +9015,7 @@
         <v>111</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D45" s="35" t="n">
         <v>0</v>
@@ -9050,7 +9053,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D46" s="35" t="n">
         <v>70</v>
@@ -9088,7 +9091,7 @@
         <v>113</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D47" s="35" t="n">
         <v>100</v>
@@ -9174,7 +9177,7 @@
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>

--- a/Objetivos/Objetivos-modelo.xlsx
+++ b/Objetivos/Objetivos-modelo.xlsx
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="362">
   <si>
     <t xml:space="preserve">Objetivos da qualidade — Como usar esta planilha</t>
   </si>
@@ -576,7 +576,7 @@
     <t xml:space="preserve">Rever a escala do pico em março.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dois entregadores extras nas sextas e nos sábados</t>
+    <t xml:space="preserve">Mais dois entregadores extras nas sextas e nos sábados</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição</t>
@@ -904,9 +904,6 @@
   </si>
   <si>
     <t xml:space="preserve">Rever a escala do pico com a entrega dos novos condomínios, em março.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mais dois entregadores extras nas sextas e nos sábados</t>
   </si>
   <si>
     <t xml:space="preserve">Estudar a compra do segundo forno, segundo item do Pareto dos atrasos.</t>
@@ -1877,11 +1874,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="6793122"/>
-        <c:axId val="15333995"/>
+        <c:axId val="82431027"/>
+        <c:axId val="15324504"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6793122"/>
+        <c:axId val="82431027"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1913,7 +1910,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15333995"/>
+        <c:crossAx val="15324504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1921,7 +1918,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15333995"/>
+        <c:axId val="15324504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1962,7 +1959,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6793122"/>
+        <c:crossAx val="82431027"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -3255,10 +3252,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14:K25" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O compromisso da política a que o objetivo responde" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D14:D25" type="list">
       <formula1>"C1,C2,C3,C4"</formula1>
       <formula2>0</formula2>
@@ -3278,6 +3271,10 @@
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I14:J25" type="decimal">
       <formula1>-1000000000</formula1>
       <formula2>1000000000</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14:K25" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -7065,7 +7062,7 @@
         <v>250</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="36" t="n">
@@ -7092,10 +7089,10 @@
         <v>107</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>253</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="36" t="n">
@@ -7113,7 +7110,7 @@
         <v>239</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L26" s="7"/>
     </row>
@@ -7122,10 +7119,10 @@
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="36" t="n">
@@ -7143,7 +7140,7 @@
         <v>231</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L27" s="7"/>
     </row>
@@ -7152,10 +7149,10 @@
         <v>108</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="36" t="n">
@@ -7173,7 +7170,7 @@
         <v>242</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L28" s="7"/>
     </row>
@@ -7182,10 +7179,10 @@
         <v>109</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>262</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="36" t="n">
@@ -7203,7 +7200,7 @@
         <v>231</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L29" s="7"/>
     </row>
@@ -7212,7 +7209,7 @@
         <v>109</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>234</v>
@@ -7233,7 +7230,7 @@
         <v>242</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -7242,7 +7239,7 @@
         <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>234</v>
@@ -7263,7 +7260,7 @@
         <v>239</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -7272,10 +7269,10 @@
         <v>111</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="36" t="n">
@@ -7293,7 +7290,7 @@
         <v>242</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L32" s="7"/>
     </row>
@@ -7302,10 +7299,10 @@
         <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="36" t="n">
@@ -7317,13 +7314,13 @@
         <v>Atrasada</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>242</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L33" s="7"/>
     </row>
@@ -7332,10 +7329,10 @@
         <v>113</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>276</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="36" t="n">
@@ -7353,7 +7350,7 @@
         <v>239</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L34" s="7"/>
     </row>
@@ -7362,10 +7359,10 @@
         <v>113</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="36" t="n">
@@ -7383,7 +7380,7 @@
         <v>242</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L35" s="7"/>
     </row>
@@ -7438,7 +7435,7 @@
         <v>107</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D39" s="35" t="n">
         <v>95</v>
@@ -7472,7 +7469,7 @@
         <v>108</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D40" s="35" t="n">
         <v>1.9</v>
@@ -7506,7 +7503,7 @@
         <v>109</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D41" s="35" t="s">
         <v>234</v>
@@ -7540,7 +7537,7 @@
         <v>110</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D42" s="35" t="n">
         <v>1.6</v>
@@ -7574,7 +7571,7 @@
         <v>111</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D43" s="35" t="n">
         <v>5</v>
@@ -7608,7 +7605,7 @@
         <v>112</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D44" s="35" t="n">
         <v>3.9</v>
@@ -7642,7 +7639,7 @@
         <v>113</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D45" s="35" t="s">
         <v>234</v>
@@ -7724,7 +7721,7 @@
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
@@ -7942,7 +7939,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -7959,7 +7956,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -7976,7 +7973,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -7993,7 +7990,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -8027,7 +8024,7 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -8044,7 +8041,7 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -8061,7 +8058,7 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -8127,7 +8124,7 @@
         <v>107</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>77</v>
@@ -8145,10 +8142,10 @@
         <v>46752</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>298</v>
       </c>
       <c r="K15" s="34" t="s">
         <v>232</v>
@@ -8163,7 +8160,7 @@
         <v>108</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>75</v>
@@ -8181,10 +8178,10 @@
         <v>46568</v>
       </c>
       <c r="I16" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="K16" s="34" t="s">
         <v>232</v>
@@ -8199,13 +8196,13 @@
         <v>109</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>97</v>
@@ -8217,7 +8214,7 @@
         <v>46752</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>142</v>
@@ -8235,7 +8232,7 @@
         <v>110</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>75</v>
@@ -8253,10 +8250,10 @@
         <v>46738</v>
       </c>
       <c r="I18" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="K18" s="34" t="s">
         <v>227</v>
@@ -8271,7 +8268,7 @@
         <v>111</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>77</v>
@@ -8289,10 +8286,10 @@
         <v>46660</v>
       </c>
       <c r="I19" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="K19" s="34" t="s">
         <v>227</v>
@@ -8307,7 +8304,7 @@
         <v>112</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>77</v>
@@ -8325,10 +8322,10 @@
         <v>46568</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K20" s="34" t="s">
         <v>232</v>
@@ -8343,13 +8340,13 @@
         <v>113</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F21" s="35" t="n">
         <v>100</v>
@@ -8361,10 +8358,10 @@
         <v>46752</v>
       </c>
       <c r="I21" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>316</v>
       </c>
       <c r="K21" s="34" t="s">
         <v>227</v>
@@ -8423,10 +8420,10 @@
         <v>107</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>318</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="36" t="n">
@@ -8441,10 +8438,10 @@
         <v>24</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L25" s="7"/>
     </row>
@@ -8453,10 +8450,10 @@
         <v>107</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>321</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="36" t="n">
@@ -8471,10 +8468,10 @@
         <v>24</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L26" s="7"/>
     </row>
@@ -8483,10 +8480,10 @@
         <v>108</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="36" t="n">
@@ -8501,10 +8498,10 @@
         <v>143</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L27" s="7"/>
     </row>
@@ -8513,10 +8510,10 @@
         <v>108</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>327</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="36" t="n">
@@ -8531,10 +8528,10 @@
         <v>24</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L28" s="7"/>
     </row>
@@ -8543,7 +8540,7 @@
         <v>109</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>234</v>
@@ -8561,10 +8558,10 @@
         <v>143</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L29" s="7"/>
     </row>
@@ -8573,10 +8570,10 @@
         <v>110</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>332</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="36" t="n">
@@ -8591,10 +8588,10 @@
         <v>143</v>
       </c>
       <c r="J30" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="L30" s="7"/>
     </row>
@@ -8603,10 +8600,10 @@
         <v>110</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>336</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="36" t="n">
@@ -8621,10 +8618,10 @@
         <v>143</v>
       </c>
       <c r="J31" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>338</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -8633,10 +8630,10 @@
         <v>110</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>340</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="36" t="n">
@@ -8651,10 +8648,10 @@
         <v>24</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L32" s="7"/>
     </row>
@@ -8663,10 +8660,10 @@
         <v>111</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="36" t="n">
@@ -8681,10 +8678,10 @@
         <v>143</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L33" s="7"/>
     </row>
@@ -8693,10 +8690,10 @@
         <v>111</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="36" t="n">
@@ -8711,10 +8708,10 @@
         <v>143</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L34" s="7"/>
     </row>
@@ -8723,10 +8720,10 @@
         <v>111</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>349</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="36" t="n">
@@ -8738,13 +8735,13 @@
         <v>Não iniciada</v>
       </c>
       <c r="I35" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L35" s="7"/>
     </row>
@@ -8753,7 +8750,7 @@
         <v>112</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>234</v>
@@ -8771,10 +8768,10 @@
         <v>143</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L36" s="7"/>
     </row>
@@ -8783,7 +8780,7 @@
         <v>113</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>234</v>
@@ -8798,13 +8795,13 @@
         <v>Não iniciada</v>
       </c>
       <c r="I37" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J37" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>354</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>355</v>
       </c>
       <c r="L37" s="7"/>
     </row>
@@ -8863,7 +8860,7 @@
         <v>107</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D41" s="35" t="n">
         <v>2.5</v>
@@ -8901,7 +8898,7 @@
         <v>108</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D42" s="35" t="n">
         <v>58</v>
@@ -8939,7 +8936,7 @@
         <v>109</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D43" s="35" t="n">
         <v>97</v>
@@ -8977,7 +8974,7 @@
         <v>110</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D44" s="35" t="n">
         <v>0</v>
@@ -9015,7 +9012,7 @@
         <v>111</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D45" s="35" t="n">
         <v>0</v>
@@ -9053,7 +9050,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D46" s="35" t="n">
         <v>70</v>
@@ -9091,7 +9088,7 @@
         <v>113</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D47" s="35" t="n">
         <v>100</v>
@@ -9177,7 +9174,7 @@
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
